--- a/Datas/Skill.xlsx
+++ b/Datas/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21045" windowHeight="8220"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -115,7 +115,7 @@
     <t>色块人的技能</t>
   </si>
   <si>
-    <t>/</t>
+    <t>Arts/UI/Prepare/Skill_3KP</t>
   </si>
   <si>
     <t>示例</t>
@@ -130,6 +130,9 @@
     <t>紫薇的技能</t>
   </si>
   <si>
+    <t>Arts/UI/Prepare/Skill_ZiWei</t>
+  </si>
+  <si>
     <t>DaMeiLiSkill</t>
   </si>
   <si>
@@ -139,6 +142,9 @@
     <t>大美丽的技能</t>
   </si>
   <si>
+    <t>Arts/UI/Prepare/Skill_DaMeiLi</t>
+  </si>
+  <si>
     <t>JinZhuangYuanSkill</t>
   </si>
   <si>
@@ -148,6 +154,9 @@
     <t>金状元的技能</t>
   </si>
   <si>
+    <t>Arts/UI/Prepare/Skill_JinZhuangYuan</t>
+  </si>
+  <si>
     <t>YaKeDongSkill</t>
   </si>
   <si>
@@ -155,6 +164,9 @@
   </si>
   <si>
     <t>亚克东的技能</t>
+  </si>
+  <si>
+    <t>Arts/UI/Prepare/Skill_YaKeDong</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1291,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -1294,19 +1306,19 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -1321,19 +1333,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -1348,19 +1360,19 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F9" s="2">
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>

--- a/Datas/Skill.xlsx
+++ b/Datas/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21045" windowHeight="8220"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -115,7 +115,7 @@
     <t>色块人的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Skill_3KP</t>
+    <t>Arts/UI/Prepare/TB_jineng_0001</t>
   </si>
   <si>
     <t>示例</t>
@@ -130,9 +130,6 @@
     <t>紫薇的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Skill_ZiWei</t>
-  </si>
-  <si>
     <t>DaMeiLiSkill</t>
   </si>
   <si>
@@ -142,7 +139,7 @@
     <t>大美丽的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Skill_DaMeiLi</t>
+    <t>Arts/UI/Prepare/TB_jineng_0002</t>
   </si>
   <si>
     <t>JinZhuangYuanSkill</t>
@@ -154,7 +151,7 @@
     <t>金状元的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Skill_JinZhuangYuan</t>
+    <t>Arts/UI/Prepare/TB_jineng_0003</t>
   </si>
   <si>
     <t>YaKeDongSkill</t>
@@ -166,7 +163,7 @@
     <t>亚克东的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Skill_YaKeDong</t>
+    <t>Arts/UI/Prepare/TB_jineng_0004</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1124,9 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="9" width="28.625" customWidth="1"/>
+    <col min="1" max="6" width="28.625" customWidth="1"/>
+    <col min="7" max="7" width="48.625" customWidth="1"/>
+    <col min="8" max="9" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9">
@@ -1291,7 +1290,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -1306,19 +1305,19 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -1333,19 +1332,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -1360,19 +1359,19 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F9" s="2">
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>

--- a/Datas/Skill.xlsx
+++ b/Datas/Skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -115,7 +115,7 @@
     <t>色块人的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/TB_jineng_0001</t>
+    <t>Arts/UI/Sprites/Gameplay/TB_huoliquankai_0001</t>
   </si>
   <si>
     <t>示例</t>
@@ -130,6 +130,9 @@
     <t>紫薇的技能</t>
   </si>
   <si>
+    <t>Arts/UI/Sprites/Gameplay/TB_bangbangwoma_0002</t>
+  </si>
+  <si>
     <t>DaMeiLiSkill</t>
   </si>
   <si>
@@ -139,7 +142,7 @@
     <t>大美丽的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/TB_jineng_0002</t>
+    <t>Arts/UI/Sprites/Gameplay/TB_aixinlaolongi_0004</t>
   </si>
   <si>
     <t>JinZhuangYuanSkill</t>
@@ -151,7 +154,7 @@
     <t>金状元的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/TB_jineng_0003</t>
+    <t>Arts/UI/Sprites/Gameplay/TB_huojiantouwei_0003</t>
   </si>
   <si>
     <t>YaKeDongSkill</t>
@@ -163,7 +166,7 @@
     <t>亚克东的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/TB_jineng_0004</t>
+    <t>Arts/UI/Sprites/Gameplay/TB_shiqianruming_0005</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1293,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -1305,19 +1308,19 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -1332,19 +1335,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -1359,19 +1362,19 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" s="2">
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>

--- a/Datas/Skill.xlsx
+++ b/Datas/Skill.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
     <t>色块人的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Sprites/Gameplay/TB_huoliquankai_0001</t>
+    <t>Assets/Arts/UI/Sprites/Common/Skills/TB_huoliquankai_0001</t>
   </si>
   <si>
     <t>示例</t>
@@ -130,7 +130,7 @@
     <t>紫薇的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Sprites/Gameplay/TB_bangbangwoma_0002</t>
+    <t>Assets/Arts/UI/Sprites/Common/Skills/TB_bangbangwoma_0002</t>
   </si>
   <si>
     <t>DaMeiLiSkill</t>
@@ -142,7 +142,7 @@
     <t>大美丽的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Sprites/Gameplay/TB_aixinlaolongi_0004</t>
+    <t>Assets/Arts/UI/Sprites/Common/Skills/TB_aixinlaolongi_0004</t>
   </si>
   <si>
     <t>JinZhuangYuanSkill</t>
@@ -154,7 +154,7 @@
     <t>金状元的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Sprites/Gameplay/TB_huojiantouwei_0003</t>
+    <t>Assets/Arts/UI/Sprites/Common/Skills/TB_huojiantouwei_0003</t>
   </si>
   <si>
     <t>YaKeDongSkill</t>
@@ -166,7 +166,7 @@
     <t>亚克东的技能</t>
   </si>
   <si>
-    <t>Arts/UI/Sprites/Gameplay/TB_shiqianruming_0005</t>
+    <t>Assets/Arts/UI/Sprites/Common/Skills/TB_shiqianruming_0005</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1128,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="6" width="28.625" customWidth="1"/>
-    <col min="7" max="7" width="48.625" customWidth="1"/>
+    <col min="7" max="7" width="78.625" customWidth="1"/>
     <col min="8" max="9" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1383,7 +1383,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:9">
+    <row r="10" customHeight="1" spans="4:9">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>

--- a/Datas/Skill.xlsx
+++ b/Datas/Skill.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -46,9 +46,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Duration</t>
-  </si>
-  <si>
     <t>IconResourcePath</t>
   </si>
   <si>
@@ -70,9 +67,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
   </si>
   <si>
     <t>技能描述</t>
-  </si>
-  <si>
-    <t>持续时间</t>
   </si>
   <si>
     <t>图标资源路径</t>
@@ -1124,15 +1115,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="6" width="28.625" customWidth="1"/>
-    <col min="7" max="7" width="78.625" customWidth="1"/>
-    <col min="8" max="9" width="28.625" customWidth="1"/>
+    <col min="1" max="5" width="28.625" customWidth="1"/>
+    <col min="6" max="6" width="78.625" customWidth="1"/>
+    <col min="7" max="8" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9">
+    <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1157,239 +1148,211 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:9">
-      <c r="A3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:9">
+    <row r="5" ht="28" customHeight="1" spans="1:8">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="2">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:9">
+    <row r="6" ht="28" customHeight="1" spans="1:8">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="2">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="G6" s="2">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>29</v>
+      <c r="H6" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9">
+    <row r="7" ht="28" customHeight="1" spans="1:8">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="2">
-        <v>10</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="2">
+      <c r="G7" s="2">
         <v>1</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>29</v>
+      <c r="H7" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:9">
+    <row r="8" ht="28" customHeight="1" spans="1:8">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="2">
-        <v>10</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="2">
+      <c r="G8" s="2">
         <v>1</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>29</v>
+      <c r="H8" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1" spans="1:9">
+    <row r="9" ht="28" customHeight="1" spans="1:8">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="2">
-        <v>10</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="G9" s="2">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>29</v>
+      <c r="H9" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="4:9">
+    <row r="10" customHeight="1" spans="1:8">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/Skill.xlsx
+++ b/Datas/Skill.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Duration</t>
+  </si>
+  <si>
     <t>IconResourcePath</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -86,6 +92,9 @@
   </si>
   <si>
     <t>技能描述</t>
+  </si>
+  <si>
+    <t>技能持续时间</t>
   </si>
   <si>
     <t>图标资源路径</t>
@@ -1115,15 +1124,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="5" width="28.625" customWidth="1"/>
-    <col min="6" max="6" width="78.625" customWidth="1"/>
-    <col min="7" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="2" width="28.625" customWidth="1"/>
+    <col min="3" max="3" width="48.625" customWidth="1"/>
+    <col min="4" max="6" width="28.625" customWidth="1"/>
+    <col min="7" max="7" width="78.625" customWidth="1"/>
+    <col min="8" max="9" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:8">
+    <row r="1" ht="28" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1148,211 +1159,239 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:8">
+    <row r="2" ht="28" customHeight="1" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
+      <c r="I2" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:8">
+    <row r="3" ht="28" customHeight="1" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:8">
+    <row r="4" ht="28" customHeight="1" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:8">
+    <row r="5" ht="28" customHeight="1" spans="1:9">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="2">
+        <v>27</v>
+      </c>
+      <c r="F5" s="2">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="2">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>26</v>
+      <c r="I5" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:8">
+    <row r="6" ht="28" customHeight="1" spans="1:9">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:8">
+    <row r="7" ht="28" customHeight="1" spans="1:9">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="2">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="2">
         <v>1</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>26</v>
+      <c r="I7" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:8">
+    <row r="8" ht="28" customHeight="1" spans="1:9">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="2">
+        <v>40</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="2">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>26</v>
+      <c r="I8" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1" spans="1:8">
+    <row r="9" ht="28" customHeight="1" spans="1:9">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="2">
+        <v>44</v>
+      </c>
+      <c r="F9" s="2">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="2">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>26</v>
+      <c r="I9" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:8">
+    <row r="10" customHeight="1" spans="4:9">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/Skill.xlsx
+++ b/Datas/Skill.xlsx
@@ -338,12 +338,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -679,7 +685,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -703,16 +709,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -721,96 +727,102 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1237,7 +1249,7 @@
       <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -1251,147 +1263,147 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:9">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <v>1</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:9">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>10</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
         <v>3</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>10</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <v>1</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
         <v>4</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>10</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="3">
         <v>1</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:9">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
         <v>5</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>10</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="3">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="4:9">
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/Skill.xlsx
+++ b/Datas/Skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>IconResourcePath</t>
-  </si>
-  <si>
     <t>ParamTableID</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>技能持续时间</t>
   </si>
   <si>
-    <t>图标资源路径</t>
-  </si>
-  <si>
     <t>参数子表ID</t>
   </si>
   <si>
@@ -115,9 +109,6 @@
     <t>色块人的技能</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Common/Skills/TB_huoliquankai_0001</t>
-  </si>
-  <si>
     <t>示例</t>
   </si>
   <si>
@@ -130,9 +121,6 @@
     <t>紫薇的技能</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Common/Skills/TB_bangbangwoma_0002</t>
-  </si>
-  <si>
     <t>DaMeiLiSkill</t>
   </si>
   <si>
@@ -142,9 +130,6 @@
     <t>大美丽的技能</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Common/Skills/TB_aixinlaolongi_0004</t>
-  </si>
-  <si>
     <t>JinZhuangYuanSkill</t>
   </si>
   <si>
@@ -154,9 +139,6 @@
     <t>金状元的技能</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Common/Skills/TB_huojiantouwei_0003</t>
-  </si>
-  <si>
     <t>YaKeDongSkill</t>
   </si>
   <si>
@@ -164,9 +146,6 @@
   </si>
   <si>
     <t>亚克东的技能</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Common/Skills/TB_shiqianruming_0005</t>
   </si>
 </sst>
 </file>
@@ -338,18 +317,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -685,7 +658,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -709,16 +682,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -727,102 +700,96 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1136,17 +1103,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="3" width="48.625" customWidth="1"/>
-    <col min="4" max="6" width="28.625" customWidth="1"/>
-    <col min="7" max="7" width="78.625" customWidth="1"/>
-    <col min="8" max="9" width="28.625" customWidth="1"/>
+    <col min="4" max="8" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9">
+    <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1171,239 +1136,211 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:8">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="2">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:8">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2">
         <v>10</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+    <row r="7" ht="28" customHeight="1" spans="1:8">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>24</v>
+    <row r="8" ht="28" customHeight="1" spans="1:8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:9">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3">
+    <row r="9" ht="28" customHeight="1" spans="1:8">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="2">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="H9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="4">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:9">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="4">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3">
-        <v>3</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="4">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:9">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="4">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:9">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="4">
-        <v>10</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="4:9">
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+    <row r="10" customHeight="1" spans="4:8">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/Skill.xlsx
+++ b/Datas/Skill.xlsx
@@ -109,7 +109,7 @@
     <t>色块人的技能</t>
   </si>
   <si>
-    <t>示例</t>
+    <t>/</t>
   </si>
   <si>
     <t>ZiWeiSkill</t>

--- a/Datas/Skill.xlsx
+++ b/Datas/Skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -52,9 +52,6 @@
     <t>ParamTableID</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -97,19 +94,13 @@
     <t>参数子表ID</t>
   </si>
   <si>
-    <t>注释</t>
-  </si>
-  <si>
     <t>_3KPSkill</t>
   </si>
   <si>
     <t>火力全开</t>
   </si>
   <si>
-    <t>色块人的技能</t>
-  </si>
-  <si>
-    <t>/</t>
+    <t>枪口喷火，子弹像下雨，打得又快又疼，动物们快跑！</t>
   </si>
   <si>
     <t>ZiWeiSkill</t>
@@ -118,7 +109,7 @@
     <t>帮帮我嘛</t>
   </si>
   <si>
-    <t>紫薇的技能</t>
+    <t>紫薇喊一声，身边护卫跟着自己打猎小动物，真省心呀！</t>
   </si>
   <si>
     <t>DaMeiLiSkill</t>
@@ -127,7 +118,7 @@
     <t>爱心牢笼</t>
   </si>
   <si>
-    <t>大美丽的技能</t>
+    <t>大美丽放爱心，小动物被圈住，跑不掉还掉血！</t>
   </si>
   <si>
     <t>JinZhuangYuanSkill</t>
@@ -136,7 +127,7 @@
     <t>火箭投喂</t>
   </si>
   <si>
-    <t>金状元的技能</t>
+    <t>火箭飞上天，又落下来，爆出满地好吃哒，大家快捡！</t>
   </si>
   <si>
     <t>YaKeDongSkill</t>
@@ -145,7 +136,7 @@
     <t>视钱如命</t>
   </si>
   <si>
-    <t>亚克东的技能</t>
+    <t>天上跑下金币小人，叮叮当当，快去捡钱，别错过！</t>
   </si>
 </sst>
 </file>
@@ -1103,15 +1094,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="3" width="48.625" customWidth="1"/>
-    <col min="4" max="8" width="28.625" customWidth="1"/>
+    <col min="4" max="4" width="28.625" customWidth="1"/>
+    <col min="5" max="5" width="59.1166666666667" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:8">
+    <row r="1" ht="28" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,101 +1126,89 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>14</v>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:8">
+    <row r="5" ht="28" customHeight="1" spans="1:7">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="F5" s="2">
         <v>10</v>
@@ -1235,23 +1216,20 @@
       <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:8">
+    <row r="6" ht="28" customHeight="1" spans="1:7">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2">
         <v>10</v>
@@ -1259,23 +1237,20 @@
       <c r="G6" s="2">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:8">
+    <row r="7" ht="28" customHeight="1" spans="1:7">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
@@ -1283,23 +1258,20 @@
       <c r="G7" s="2">
         <v>1</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:8">
+    <row r="8" ht="28" customHeight="1" spans="1:7">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
@@ -1307,23 +1279,20 @@
       <c r="G8" s="2">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="9" ht="28" customHeight="1" spans="1:8">
+    <row r="9" ht="28" customHeight="1" spans="1:7">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F9" s="2">
         <v>10</v>
@@ -1331,16 +1300,12 @@
       <c r="G9" s="2">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="10" customHeight="1" spans="4:8">
+    <row r="10" customHeight="1" spans="4:7">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
